--- a/script/mappa_variabili.xlsx
+++ b/script/mappa_variabili.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SCUOLA\3.RICERCA\1. Fellowship\UNIBO\Fellowship\Pharmacovigilance\Std_dati_nefrologia\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5D27B0-37C2-41B9-9065-329354B01A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3D1495-6826-4713-B18C-51242FDAE1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-855" windowWidth="19440" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mappa_variabili" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>variabile_sorgente</t>
   </si>
@@ -163,9 +163,6 @@
     <t>Matching sinonimi/radici con esclusione negazioni, familiarità, incertezza e alcune condizioni esplicitamente risolte</t>
   </si>
   <si>
-    <t>Categorie specifiche aggiunte dopo revisione esperta: diabete non specificato, retinopatia, glaucoma, nefropatia, infarto miocardico e IVU</t>
-  </si>
-  <si>
     <t>testo_comorbidita_originale</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
     <t>farmaco_pre</t>
   </si>
   <si>
-    <t>Riconoscimento del principio attivo privilegiando il farmaco menzionato per primo; le combinazioni possono essere esplose in più righe</t>
-  </si>
-  <si>
     <t>Riduce falsi match dovuti a farmaci citati in note/avvertenze; esempio: tiamazolo vs paracetamolo</t>
   </si>
   <si>
@@ -292,7 +286,7 @@
     <t>consiglio_clinico</t>
   </si>
   <si>
-    <t>Matching conseguenze standard con ampliamento delle formulazioni di prolungamento QT</t>
+    <t>Riconoscimento del principio attivo privilegiando il farmaco menzionato per primo; le combinazioni possono essere in più righe</t>
   </si>
 </sst>
 </file>
@@ -340,10 +334,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -826,9 +820,7 @@
       <c r="E14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -838,14 +830,14 @@
         <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -853,13 +845,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -869,19 +861,19 @@
         <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -889,13 +881,13 @@
         <v>29</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>39</v>
@@ -907,17 +899,17 @@
         <v>29</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -925,13 +917,13 @@
         <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -941,17 +933,17 @@
         <v>29</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -959,13 +951,13 @@
         <v>29</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -975,47 +967,47 @@
         <v>29</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1025,103 +1017,103 @@
         <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
